--- a/OtherAnalyses/Raji/data/data_counts_cleaned.xlsx
+++ b/OtherAnalyses/Raji/data/data_counts_cleaned.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11130"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Leander\Documents\Papers_manuscripts\MGAT5\MGAT5KO_CART_manuscript\Raji\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Leander/Documents/Papers_manuscripts/MGAT5/MGAT5KO_CART_manuscript/OtherAnalyses/Raji/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BCBCC3F-6A26-4CEA-B983-B2CE72B33239}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E01209F1-E217-7247-9507-29D931AF6188}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-11520" yWindow="-21600" windowWidth="25800" windowHeight="21000" xr2:uid="{47F8F176-BF44-4A4C-9CFE-0EC8B11B1CF1}"/>
+    <workbookView xWindow="-13060" yWindow="-28180" windowWidth="29060" windowHeight="28180" xr2:uid="{47F8F176-BF44-4A4C-9CFE-0EC8B11B1CF1}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029" iterateDelta="1E-4"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="30">
   <si>
     <t>Experiment</t>
   </si>
@@ -91,12 +91,48 @@
   <si>
     <t>CellCount_pul</t>
   </si>
+  <si>
+    <t>TumorPresent</t>
+  </si>
+  <si>
+    <t>Day_TumorAppearance</t>
+  </si>
+  <si>
+    <t>Day_TumorDisappearance</t>
+  </si>
+  <si>
+    <t>Day_TumorRelapse</t>
+  </si>
+  <si>
+    <t>Day_SecondaryTumorAppearance</t>
+  </si>
+  <si>
+    <t>E91</t>
+  </si>
+  <si>
+    <t>CD19 CAR - mock</t>
+  </si>
+  <si>
+    <t>CD19 CAR - MGAT5 KO</t>
+  </si>
+  <si>
+    <t>E97</t>
+  </si>
+  <si>
+    <t>No Raji - CD19 CAR mock</t>
+  </si>
+  <si>
+    <t>No Raji - CD19 CAR MGAT5 KO</t>
+  </si>
+  <si>
+    <t>No Raji - NTC</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="21" x14ac:knownFonts="1">
+  <fonts count="22" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -250,6 +286,12 @@
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="33">
@@ -595,8 +637,13 @@
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="44">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -974,17 +1021,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{28924032-712C-42DD-811A-811BE3665EE3}">
-  <dimension ref="A1:E98"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:J161"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.7109375" customWidth="1"/>
-    <col min="4" max="4" width="34" customWidth="1"/>
-    <col min="5" max="5" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.83203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.6640625" customWidth="1"/>
+    <col min="4" max="4" width="30.5" customWidth="1"/>
+    <col min="5" max="5" width="17" customWidth="1"/>
+    <col min="6" max="6" width="13.5" customWidth="1"/>
+    <col min="7" max="7" width="21.83203125" customWidth="1"/>
+    <col min="8" max="8" width="24.6640625" customWidth="1"/>
+    <col min="9" max="9" width="18.1640625" customWidth="1"/>
+    <col min="10" max="10" width="11.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1000,8 +1052,23 @@
       <c r="E1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I1" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -1009,84 +1076,124 @@
         <v>21</v>
       </c>
       <c r="C2">
+        <v>2</v>
+      </c>
+      <c r="D2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E2">
+        <v>2.34375</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="G2">
+        <v>11</v>
+      </c>
+      <c r="H2" s="1"/>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3">
+        <v>21</v>
+      </c>
+      <c r="C3">
+        <v>3</v>
+      </c>
+      <c r="D3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E3">
+        <v>1040.168776371308</v>
+      </c>
+      <c r="F3" s="2">
+        <v>1</v>
+      </c>
+      <c r="G3">
+        <v>11</v>
+      </c>
+      <c r="H3" s="1">
+        <v>22</v>
+      </c>
+      <c r="I3">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4">
+        <v>21</v>
+      </c>
+      <c r="C4">
+        <v>4</v>
+      </c>
+      <c r="D4" t="s">
+        <v>4</v>
+      </c>
+      <c r="E4">
+        <v>939.82737361282375</v>
+      </c>
+      <c r="F4">
+        <v>1</v>
+      </c>
+      <c r="G4">
+        <v>11</v>
+      </c>
+      <c r="H4" s="1"/>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B5">
+        <v>21</v>
+      </c>
+      <c r="C5">
+        <v>5</v>
+      </c>
+      <c r="D5" t="s">
+        <v>5</v>
+      </c>
+      <c r="E5">
+        <v>142.58632362897765</v>
+      </c>
+      <c r="F5">
+        <v>1</v>
+      </c>
+      <c r="G5">
+        <v>11</v>
+      </c>
+      <c r="H5" s="1"/>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>1</v>
+      </c>
+      <c r="B6">
+        <v>21</v>
+      </c>
+      <c r="C6">
         <v>6</v>
-      </c>
-      <c r="D2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E2">
-        <v>133.12434691745037</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3">
-        <v>21</v>
-      </c>
-      <c r="C3">
-        <v>16</v>
-      </c>
-      <c r="D3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E3">
-        <v>132.69230769230768</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>1</v>
-      </c>
-      <c r="B4">
-        <v>21</v>
-      </c>
-      <c r="C4">
-        <v>27</v>
-      </c>
-      <c r="D4" t="s">
-        <v>6</v>
-      </c>
-      <c r="E4">
-        <v>403.51170568561872</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B5">
-        <v>21</v>
-      </c>
-      <c r="C5">
-        <v>37</v>
-      </c>
-      <c r="D5" t="s">
-        <v>6</v>
-      </c>
-      <c r="E5">
-        <v>152.45283018867926</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>1</v>
-      </c>
-      <c r="B6">
-        <v>21</v>
-      </c>
-      <c r="C6">
-        <v>43</v>
       </c>
       <c r="D6" t="s">
         <v>6</v>
       </c>
       <c r="E6">
-        <v>37.904015670910873</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+        <v>133.12434691745037</v>
+      </c>
+      <c r="F6">
+        <v>1</v>
+      </c>
+      <c r="G6">
+        <v>11</v>
+      </c>
+      <c r="H6" s="1"/>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>1</v>
       </c>
@@ -1094,16 +1201,23 @@
         <v>21</v>
       </c>
       <c r="C7">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D7" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E7">
-        <v>939.82737361282375</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+        <v>1.9279128248113997</v>
+      </c>
+      <c r="F7">
+        <v>1</v>
+      </c>
+      <c r="G7">
+        <v>11</v>
+      </c>
+      <c r="H7" s="1"/>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>1</v>
       </c>
@@ -1111,16 +1225,23 @@
         <v>21</v>
       </c>
       <c r="C8">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D8" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E8">
-        <v>469.68641114982574</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+        <v>497.97930014785612</v>
+      </c>
+      <c r="F8">
+        <v>1</v>
+      </c>
+      <c r="G8">
+        <v>11</v>
+      </c>
+      <c r="H8" s="1"/>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>1</v>
       </c>
@@ -1128,101 +1249,145 @@
         <v>21</v>
       </c>
       <c r="C9">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="D9" t="s">
         <v>4</v>
       </c>
       <c r="E9">
+        <v>469.68641114982574</v>
+      </c>
+      <c r="F9" s="2">
+        <v>1</v>
+      </c>
+      <c r="G9">
+        <v>11</v>
+      </c>
+      <c r="H9" s="1">
+        <v>28</v>
+      </c>
+      <c r="I9">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>1</v>
+      </c>
+      <c r="B10">
+        <v>21</v>
+      </c>
+      <c r="C10">
+        <v>15</v>
+      </c>
+      <c r="D10" t="s">
+        <v>5</v>
+      </c>
+      <c r="E10">
+        <v>64.997914059240713</v>
+      </c>
+      <c r="F10">
+        <v>1</v>
+      </c>
+      <c r="G10">
+        <v>11</v>
+      </c>
+      <c r="H10" s="1"/>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>1</v>
+      </c>
+      <c r="B11">
+        <v>21</v>
+      </c>
+      <c r="C11">
+        <v>16</v>
+      </c>
+      <c r="D11" t="s">
+        <v>6</v>
+      </c>
+      <c r="E11">
+        <v>132.69230769230768</v>
+      </c>
+      <c r="F11">
+        <v>1</v>
+      </c>
+      <c r="G11">
+        <v>11</v>
+      </c>
+      <c r="H11" s="1"/>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>1</v>
+      </c>
+      <c r="B12">
+        <v>21</v>
+      </c>
+      <c r="C12">
+        <v>21</v>
+      </c>
+      <c r="D12" t="s">
+        <v>7</v>
+      </c>
+      <c r="E12">
+        <v>0.16680567139282734</v>
+      </c>
+      <c r="F12">
+        <v>0</v>
+      </c>
+      <c r="H12" s="1"/>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>1</v>
+      </c>
+      <c r="B13">
+        <v>21</v>
+      </c>
+      <c r="C13">
+        <v>24</v>
+      </c>
+      <c r="D13" t="s">
+        <v>3</v>
+      </c>
+      <c r="E13">
+        <v>360.65979381443299</v>
+      </c>
+      <c r="F13" s="2">
+        <v>1</v>
+      </c>
+      <c r="G13">
+        <v>11</v>
+      </c>
+      <c r="H13" s="1"/>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>1</v>
+      </c>
+      <c r="B14">
+        <v>21</v>
+      </c>
+      <c r="C14">
+        <v>25</v>
+      </c>
+      <c r="D14" t="s">
+        <v>4</v>
+      </c>
+      <c r="E14">
         <v>440.96000000000004</v>
       </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>1</v>
-      </c>
-      <c r="B10">
-        <v>21</v>
-      </c>
-      <c r="C10">
-        <v>35</v>
-      </c>
-      <c r="D10" t="s">
-        <v>4</v>
-      </c>
-      <c r="E10">
-        <v>271.68458781362006</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>1</v>
-      </c>
-      <c r="B11">
-        <v>21</v>
-      </c>
-      <c r="C11">
-        <v>5</v>
-      </c>
-      <c r="D11" t="s">
-        <v>5</v>
-      </c>
-      <c r="E11">
-        <v>142.58632362897765</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>1</v>
-      </c>
-      <c r="B12">
-        <v>21</v>
-      </c>
-      <c r="C12">
-        <v>15</v>
-      </c>
-      <c r="D12" t="s">
-        <v>5</v>
-      </c>
-      <c r="E12">
-        <v>64.997914059240713</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>1</v>
-      </c>
-      <c r="B13">
-        <v>21</v>
-      </c>
-      <c r="C13">
-        <v>26</v>
-      </c>
-      <c r="D13" t="s">
-        <v>5</v>
-      </c>
-      <c r="E13">
-        <v>56.399132321041215</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>1</v>
-      </c>
-      <c r="B14">
-        <v>21</v>
-      </c>
-      <c r="C14">
-        <v>36</v>
-      </c>
-      <c r="D14" t="s">
-        <v>5</v>
-      </c>
-      <c r="E14">
-        <v>116.10273134936813</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F14">
+        <v>1</v>
+      </c>
+      <c r="G14">
+        <v>11</v>
+      </c>
+      <c r="H14" s="1"/>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>1</v>
       </c>
@@ -1230,16 +1395,23 @@
         <v>21</v>
       </c>
       <c r="C15">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="D15" t="s">
         <v>5</v>
       </c>
       <c r="E15">
-        <v>144.60921843687376</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+        <v>56.399132321041215</v>
+      </c>
+      <c r="F15">
+        <v>1</v>
+      </c>
+      <c r="G15">
+        <v>11</v>
+      </c>
+      <c r="H15" s="1"/>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>1</v>
       </c>
@@ -1247,16 +1419,23 @@
         <v>21</v>
       </c>
       <c r="C16">
-        <v>3</v>
+        <v>27</v>
       </c>
       <c r="D16" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E16">
-        <v>1040.168776371308</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+        <v>403.51170568561872</v>
+      </c>
+      <c r="F16">
+        <v>1</v>
+      </c>
+      <c r="G16">
+        <v>11</v>
+      </c>
+      <c r="H16" s="1"/>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>1</v>
       </c>
@@ -1264,16 +1443,23 @@
         <v>21</v>
       </c>
       <c r="C17">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="D17" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E17">
-        <v>497.97930014785612</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+        <v>0.79575596816976124</v>
+      </c>
+      <c r="F17">
+        <v>1</v>
+      </c>
+      <c r="G17">
+        <v>11</v>
+      </c>
+      <c r="H17" s="1"/>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>1</v>
       </c>
@@ -1281,16 +1467,23 @@
         <v>21</v>
       </c>
       <c r="C18">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="D18" t="s">
         <v>3</v>
       </c>
       <c r="E18">
-        <v>360.65979381443299</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+        <v>767.72965254640644</v>
+      </c>
+      <c r="F18">
+        <v>1</v>
+      </c>
+      <c r="G18">
+        <v>11</v>
+      </c>
+      <c r="H18" s="1"/>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>1</v>
       </c>
@@ -1298,16 +1491,23 @@
         <v>21</v>
       </c>
       <c r="C19">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D19" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E19">
-        <v>767.72965254640644</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+        <v>271.68458781362006</v>
+      </c>
+      <c r="F19">
+        <v>1</v>
+      </c>
+      <c r="G19">
+        <v>11</v>
+      </c>
+      <c r="H19" s="1"/>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>1</v>
       </c>
@@ -1315,135 +1515,182 @@
         <v>21</v>
       </c>
       <c r="C20">
+        <v>36</v>
+      </c>
+      <c r="D20" t="s">
+        <v>5</v>
+      </c>
+      <c r="E20">
+        <v>116.10273134936813</v>
+      </c>
+      <c r="F20">
+        <v>1</v>
+      </c>
+      <c r="G20">
+        <v>11</v>
+      </c>
+      <c r="H20" s="1"/>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
+        <v>1</v>
+      </c>
+      <c r="B21">
+        <v>21</v>
+      </c>
+      <c r="C21">
+        <v>37</v>
+      </c>
+      <c r="D21" t="s">
+        <v>6</v>
+      </c>
+      <c r="E21">
+        <v>152.45283018867926</v>
+      </c>
+      <c r="F21">
+        <v>1</v>
+      </c>
+      <c r="G21">
+        <v>11</v>
+      </c>
+      <c r="H21" s="1"/>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A22" t="s">
+        <v>1</v>
+      </c>
+      <c r="B22">
+        <v>21</v>
+      </c>
+      <c r="C22">
+        <v>42</v>
+      </c>
+      <c r="D22" t="s">
+        <v>5</v>
+      </c>
+      <c r="E22">
+        <v>144.60921843687376</v>
+      </c>
+      <c r="F22">
+        <v>1</v>
+      </c>
+      <c r="G22">
+        <v>11</v>
+      </c>
+      <c r="H22" s="1"/>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A23" t="s">
+        <v>1</v>
+      </c>
+      <c r="B23">
+        <v>21</v>
+      </c>
+      <c r="C23">
+        <v>43</v>
+      </c>
+      <c r="D23" t="s">
+        <v>6</v>
+      </c>
+      <c r="E23">
+        <v>37.904015670910873</v>
+      </c>
+      <c r="F23">
+        <v>1</v>
+      </c>
+      <c r="G23">
+        <v>11</v>
+      </c>
+      <c r="H23" s="1"/>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A24" t="s">
+        <v>1</v>
+      </c>
+      <c r="B24">
+        <v>92</v>
+      </c>
+      <c r="C24">
+        <v>21</v>
+      </c>
+      <c r="D24" t="s">
+        <v>7</v>
+      </c>
+      <c r="E24">
+        <v>0.02</v>
+      </c>
+      <c r="F24">
+        <v>0</v>
+      </c>
+      <c r="H24" s="1"/>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A25" t="s">
+        <v>1</v>
+      </c>
+      <c r="B25">
+        <v>154</v>
+      </c>
+      <c r="C25">
+        <v>21</v>
+      </c>
+      <c r="D25" t="s">
+        <v>7</v>
+      </c>
+      <c r="E25">
+        <v>0.05</v>
+      </c>
+      <c r="F25">
+        <v>0</v>
+      </c>
+      <c r="H25" s="1"/>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A26" t="s">
+        <v>11</v>
+      </c>
+      <c r="B26">
+        <v>21</v>
+      </c>
+      <c r="C26" s="3">
+        <v>1</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E26">
+        <v>0.05</v>
+      </c>
+      <c r="F26">
+        <v>1</v>
+      </c>
+      <c r="G26">
+        <v>14</v>
+      </c>
+      <c r="H26" s="1"/>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A27" t="s">
+        <v>11</v>
+      </c>
+      <c r="B27">
+        <v>21</v>
+      </c>
+      <c r="C27">
         <v>2</v>
       </c>
-      <c r="D20" t="s">
-        <v>2</v>
-      </c>
-      <c r="E20">
-        <v>2.34375</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>1</v>
-      </c>
-      <c r="B21">
-        <v>21</v>
-      </c>
-      <c r="C21">
-        <v>8</v>
-      </c>
-      <c r="D21" t="s">
-        <v>2</v>
-      </c>
-      <c r="E21">
-        <v>1.9279128248113997</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>1</v>
-      </c>
-      <c r="B22">
-        <v>21</v>
-      </c>
-      <c r="C22">
-        <v>29</v>
-      </c>
-      <c r="D22" t="s">
-        <v>2</v>
-      </c>
-      <c r="E22">
-        <v>0.79575596816976124</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>16</v>
-      </c>
-      <c r="B23">
-        <v>21</v>
-      </c>
-      <c r="C23">
-        <v>5</v>
-      </c>
-      <c r="D23" t="s">
-        <v>2</v>
-      </c>
-      <c r="E23">
-        <v>0.24</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>16</v>
-      </c>
-      <c r="B24">
-        <v>21</v>
-      </c>
-      <c r="C24">
-        <v>8</v>
-      </c>
-      <c r="D24" t="s">
-        <v>2</v>
-      </c>
-      <c r="E24">
-        <v>0.03</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>16</v>
-      </c>
-      <c r="B25">
-        <v>21</v>
-      </c>
-      <c r="C25">
-        <v>35</v>
-      </c>
-      <c r="D25" t="s">
-        <v>2</v>
-      </c>
-      <c r="E25">
+      <c r="D27" t="s">
+        <v>13</v>
+      </c>
+      <c r="E27">
+        <v>0.63</v>
+      </c>
+      <c r="F27">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>16</v>
-      </c>
-      <c r="B26">
-        <v>21</v>
-      </c>
-      <c r="C26">
-        <v>40</v>
-      </c>
-      <c r="D26" t="s">
-        <v>2</v>
-      </c>
-      <c r="E26">
-        <v>0.01</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>16</v>
-      </c>
-      <c r="B27">
-        <v>21</v>
-      </c>
-      <c r="C27">
-        <v>41</v>
-      </c>
-      <c r="D27" t="s">
-        <v>2</v>
-      </c>
-      <c r="E27">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="H27" s="1"/>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>11</v>
       </c>
@@ -1459,98 +1706,144 @@
       <c r="E28">
         <v>1.06</v>
       </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F28">
+        <v>1</v>
+      </c>
+      <c r="G28">
+        <v>18</v>
+      </c>
+      <c r="H28" s="1">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>11</v>
       </c>
       <c r="B29">
         <v>21</v>
       </c>
-      <c r="C29">
-        <v>11</v>
+      <c r="C29" s="3">
+        <v>10</v>
       </c>
       <c r="D29" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E29">
+        <v>0.32</v>
+      </c>
+      <c r="F29">
+        <v>0</v>
+      </c>
+      <c r="G29">
+        <v>64</v>
+      </c>
+      <c r="H29" s="1"/>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A30" t="s">
+        <v>11</v>
+      </c>
+      <c r="B30">
+        <v>21</v>
+      </c>
+      <c r="C30">
+        <v>11</v>
+      </c>
+      <c r="D30" t="s">
+        <v>14</v>
+      </c>
+      <c r="E30">
         <v>4.95</v>
       </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>11</v>
-      </c>
-      <c r="B30">
-        <v>21</v>
-      </c>
-      <c r="C30">
-        <v>20</v>
-      </c>
-      <c r="D30" t="s">
-        <v>14</v>
-      </c>
-      <c r="E30">
-        <v>11.21</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F30">
+        <v>0</v>
+      </c>
+      <c r="G30">
+        <v>14</v>
+      </c>
+      <c r="H30" s="1">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>11</v>
       </c>
       <c r="B31">
         <v>21</v>
       </c>
-      <c r="C31">
-        <v>29</v>
-      </c>
-      <c r="D31" t="s">
-        <v>14</v>
+      <c r="C31" s="3">
+        <v>14</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>12</v>
       </c>
       <c r="E31">
-        <v>3.1</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+        <v>0.02</v>
+      </c>
+      <c r="F31">
+        <v>1</v>
+      </c>
+      <c r="G31">
+        <v>11</v>
+      </c>
+      <c r="H31" s="1"/>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>11</v>
       </c>
       <c r="B32">
         <v>21</v>
       </c>
-      <c r="C32">
-        <v>33</v>
-      </c>
-      <c r="D32" t="s">
-        <v>14</v>
+      <c r="C32" s="3">
+        <v>17</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>12</v>
       </c>
       <c r="E32">
-        <v>3.24</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+        <v>0.05</v>
+      </c>
+      <c r="F32">
+        <v>1</v>
+      </c>
+      <c r="G32">
+        <v>14</v>
+      </c>
+      <c r="H32" s="1"/>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>11</v>
       </c>
       <c r="B33">
-        <v>89</v>
-      </c>
-      <c r="C33">
-        <v>5</v>
+        <v>21</v>
+      </c>
+      <c r="C33" s="3">
+        <v>19</v>
       </c>
       <c r="D33" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E33">
-        <v>0.73</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+        <v>1.37</v>
+      </c>
+      <c r="F33">
+        <v>1</v>
+      </c>
+      <c r="G33">
+        <v>14</v>
+      </c>
+      <c r="H33" s="1"/>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>11</v>
       </c>
       <c r="B34">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="C34">
         <v>20</v>
@@ -1559,15 +1852,19 @@
         <v>14</v>
       </c>
       <c r="E34">
-        <v>14.22</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+        <v>11.21</v>
+      </c>
+      <c r="F34">
+        <v>0</v>
+      </c>
+      <c r="H34" s="1"/>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>11</v>
       </c>
       <c r="B35">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="C35">
         <v>29</v>
@@ -1576,724 +1873,1041 @@
         <v>14</v>
       </c>
       <c r="E35">
+        <v>3.1</v>
+      </c>
+      <c r="F35">
+        <v>0</v>
+      </c>
+      <c r="H35" s="1"/>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A36" t="s">
+        <v>11</v>
+      </c>
+      <c r="B36">
+        <v>21</v>
+      </c>
+      <c r="C36" s="3">
+        <v>30</v>
+      </c>
+      <c r="D36" t="s">
+        <v>13</v>
+      </c>
+      <c r="E36">
+        <v>1.63</v>
+      </c>
+      <c r="F36">
+        <v>0</v>
+      </c>
+      <c r="H36" s="1"/>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A37" t="s">
+        <v>11</v>
+      </c>
+      <c r="B37">
+        <v>21</v>
+      </c>
+      <c r="C37">
+        <v>31</v>
+      </c>
+      <c r="D37" t="s">
+        <v>12</v>
+      </c>
+      <c r="E37">
+        <v>0.02</v>
+      </c>
+      <c r="F37">
+        <v>1</v>
+      </c>
+      <c r="G37">
+        <v>11</v>
+      </c>
+      <c r="H37" s="1"/>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A38" t="s">
+        <v>11</v>
+      </c>
+      <c r="B38">
+        <v>21</v>
+      </c>
+      <c r="C38">
+        <v>33</v>
+      </c>
+      <c r="D38" t="s">
+        <v>14</v>
+      </c>
+      <c r="E38">
+        <v>3.24</v>
+      </c>
+      <c r="F38">
+        <v>0</v>
+      </c>
+      <c r="H38" s="1"/>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A39" t="s">
+        <v>11</v>
+      </c>
+      <c r="B39">
+        <v>89</v>
+      </c>
+      <c r="C39" s="3">
+        <v>2</v>
+      </c>
+      <c r="D39" t="s">
+        <v>13</v>
+      </c>
+      <c r="E39">
+        <v>0.59</v>
+      </c>
+      <c r="F39">
+        <v>0</v>
+      </c>
+      <c r="H39" s="1"/>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A40" t="s">
+        <v>11</v>
+      </c>
+      <c r="B40">
+        <v>89</v>
+      </c>
+      <c r="C40">
+        <v>5</v>
+      </c>
+      <c r="D40" t="s">
+        <v>14</v>
+      </c>
+      <c r="E40">
+        <v>0.73</v>
+      </c>
+      <c r="F40">
+        <v>0</v>
+      </c>
+      <c r="G40">
+        <v>18</v>
+      </c>
+      <c r="H40" s="1">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A41" t="s">
+        <v>11</v>
+      </c>
+      <c r="B41">
+        <v>89</v>
+      </c>
+      <c r="C41" s="3">
+        <v>10</v>
+      </c>
+      <c r="D41" t="s">
+        <v>13</v>
+      </c>
+      <c r="E41">
+        <v>0.36</v>
+      </c>
+      <c r="F41">
+        <v>1</v>
+      </c>
+      <c r="G41">
+        <v>64</v>
+      </c>
+      <c r="H41" s="1"/>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A42" t="s">
+        <v>11</v>
+      </c>
+      <c r="B42">
+        <v>89</v>
+      </c>
+      <c r="C42">
+        <v>20</v>
+      </c>
+      <c r="D42" t="s">
+        <v>14</v>
+      </c>
+      <c r="E42">
+        <v>14.22</v>
+      </c>
+      <c r="F42">
+        <v>0</v>
+      </c>
+      <c r="H42" s="1"/>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A43" t="s">
+        <v>11</v>
+      </c>
+      <c r="B43">
+        <v>89</v>
+      </c>
+      <c r="C43">
+        <v>29</v>
+      </c>
+      <c r="D43" t="s">
+        <v>14</v>
+      </c>
+      <c r="E43">
         <v>7.8</v>
       </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
-        <v>11</v>
-      </c>
-      <c r="B36">
+      <c r="F43">
+        <v>0</v>
+      </c>
+      <c r="H43" s="1"/>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A44" t="s">
+        <v>11</v>
+      </c>
+      <c r="B44">
         <v>89</v>
       </c>
-      <c r="C36">
+      <c r="C44" s="3">
+        <v>30</v>
+      </c>
+      <c r="D44" t="s">
+        <v>13</v>
+      </c>
+      <c r="E44">
+        <v>13.8</v>
+      </c>
+      <c r="F44">
+        <v>0</v>
+      </c>
+      <c r="H44" s="1"/>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A45" t="s">
+        <v>11</v>
+      </c>
+      <c r="B45">
+        <v>89</v>
+      </c>
+      <c r="C45">
         <v>33</v>
       </c>
-      <c r="D36" t="s">
-        <v>14</v>
-      </c>
-      <c r="E36">
+      <c r="D45" t="s">
+        <v>14</v>
+      </c>
+      <c r="E45">
         <v>0.85</v>
       </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
+      <c r="F45">
+        <v>0</v>
+      </c>
+      <c r="H45" s="1"/>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A46" t="s">
         <v>15</v>
       </c>
-      <c r="B37">
+      <c r="B46">
         <v>25</v>
       </c>
-      <c r="C37">
+      <c r="C46">
         <v>2</v>
       </c>
-      <c r="D37" t="s">
-        <v>14</v>
-      </c>
-      <c r="E37">
+      <c r="D46" t="s">
+        <v>14</v>
+      </c>
+      <c r="E46">
         <v>23.19</v>
       </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
+      <c r="F46">
+        <v>0</v>
+      </c>
+      <c r="G46">
+        <v>11</v>
+      </c>
+      <c r="H46" s="1">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A47" t="s">
         <v>15</v>
       </c>
-      <c r="B38">
+      <c r="B47">
         <v>25</v>
       </c>
-      <c r="C38">
+      <c r="C47">
+        <v>9</v>
+      </c>
+      <c r="D47" t="s">
         <v>12</v>
       </c>
-      <c r="D38" t="s">
-        <v>14</v>
-      </c>
-      <c r="E38">
+      <c r="E47">
+        <v>0.22</v>
+      </c>
+      <c r="F47">
+        <v>1</v>
+      </c>
+      <c r="G47">
+        <v>11</v>
+      </c>
+      <c r="H47" s="1"/>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A48" t="s">
+        <v>15</v>
+      </c>
+      <c r="B48">
+        <v>25</v>
+      </c>
+      <c r="C48">
+        <v>11</v>
+      </c>
+      <c r="D48" t="s">
+        <v>13</v>
+      </c>
+      <c r="E48">
+        <v>9.9600000000000009</v>
+      </c>
+      <c r="F48">
+        <v>1</v>
+      </c>
+      <c r="G48">
+        <v>11</v>
+      </c>
+      <c r="H48" s="1"/>
+    </row>
+    <row r="49" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A49" t="s">
+        <v>15</v>
+      </c>
+      <c r="B49">
+        <v>25</v>
+      </c>
+      <c r="C49">
+        <v>12</v>
+      </c>
+      <c r="D49" t="s">
+        <v>14</v>
+      </c>
+      <c r="E49">
         <v>25.43</v>
       </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
+      <c r="F49">
+        <v>0</v>
+      </c>
+      <c r="G49">
+        <v>11</v>
+      </c>
+      <c r="H49" s="1">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A50" t="s">
         <v>15</v>
       </c>
-      <c r="B39">
+      <c r="B50">
         <v>25</v>
       </c>
-      <c r="C39">
+      <c r="C50">
+        <v>16</v>
+      </c>
+      <c r="D50" t="s">
+        <v>13</v>
+      </c>
+      <c r="E50">
+        <v>11.14</v>
+      </c>
+      <c r="F50">
+        <v>0</v>
+      </c>
+      <c r="G50">
+        <v>11</v>
+      </c>
+      <c r="H50" s="1">
+        <v>19</v>
+      </c>
+      <c r="I50">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A51" t="s">
+        <v>15</v>
+      </c>
+      <c r="B51">
+        <v>25</v>
+      </c>
+      <c r="C51">
+        <v>23</v>
+      </c>
+      <c r="D51" t="s">
+        <v>13</v>
+      </c>
+      <c r="E51">
+        <v>7.73</v>
+      </c>
+      <c r="F51">
+        <v>1</v>
+      </c>
+      <c r="G51">
+        <v>11</v>
+      </c>
+      <c r="H51" s="1"/>
+    </row>
+    <row r="52" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A52" t="s">
+        <v>15</v>
+      </c>
+      <c r="B52">
+        <v>25</v>
+      </c>
+      <c r="C52">
         <v>24</v>
       </c>
-      <c r="D39" t="s">
-        <v>14</v>
-      </c>
-      <c r="E39">
+      <c r="D52" t="s">
+        <v>14</v>
+      </c>
+      <c r="E52">
         <v>38.54</v>
       </c>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
+      <c r="F52" s="2">
+        <v>1</v>
+      </c>
+      <c r="G52">
+        <v>11</v>
+      </c>
+      <c r="H52" s="1">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A53" t="s">
         <v>15</v>
       </c>
-      <c r="B40">
+      <c r="B53">
         <v>25</v>
       </c>
-      <c r="C40">
+      <c r="C53">
+        <v>29</v>
+      </c>
+      <c r="D53" t="s">
+        <v>13</v>
+      </c>
+      <c r="E53">
+        <v>13.1</v>
+      </c>
+      <c r="F53">
+        <v>1</v>
+      </c>
+      <c r="G53">
+        <v>11</v>
+      </c>
+      <c r="H53" s="1"/>
+    </row>
+    <row r="54" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A54" t="s">
+        <v>15</v>
+      </c>
+      <c r="B54">
+        <v>25</v>
+      </c>
+      <c r="C54">
         <v>30</v>
       </c>
-      <c r="D40" t="s">
-        <v>14</v>
-      </c>
-      <c r="E40">
+      <c r="D54" t="s">
+        <v>14</v>
+      </c>
+      <c r="E54">
         <v>76.540000000000006</v>
       </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
+      <c r="F54">
+        <v>0</v>
+      </c>
+      <c r="G54">
+        <v>11</v>
+      </c>
+      <c r="H54" s="1">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A55" t="s">
         <v>15</v>
       </c>
-      <c r="B41">
+      <c r="B55">
+        <v>25</v>
+      </c>
+      <c r="C55">
+        <v>35</v>
+      </c>
+      <c r="D55" t="s">
+        <v>12</v>
+      </c>
+      <c r="E55">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="F55">
+        <v>1</v>
+      </c>
+      <c r="G55">
+        <v>11</v>
+      </c>
+      <c r="H55" s="1"/>
+    </row>
+    <row r="56" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A56" t="s">
+        <v>15</v>
+      </c>
+      <c r="B56">
+        <v>25</v>
+      </c>
+      <c r="C56">
+        <v>36</v>
+      </c>
+      <c r="D56" t="s">
+        <v>13</v>
+      </c>
+      <c r="E56">
+        <v>23</v>
+      </c>
+      <c r="F56">
+        <v>1</v>
+      </c>
+      <c r="G56">
+        <v>11</v>
+      </c>
+      <c r="H56" s="1"/>
+    </row>
+    <row r="57" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A57" t="s">
+        <v>15</v>
+      </c>
+      <c r="B57">
+        <v>25</v>
+      </c>
+      <c r="C57">
+        <v>37</v>
+      </c>
+      <c r="D57" t="s">
+        <v>12</v>
+      </c>
+      <c r="E57">
+        <v>0.19</v>
+      </c>
+      <c r="F57">
+        <v>1</v>
+      </c>
+      <c r="G57">
+        <v>11</v>
+      </c>
+      <c r="H57" s="1"/>
+    </row>
+    <row r="58" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A58" t="s">
+        <v>15</v>
+      </c>
+      <c r="B58">
         <v>88</v>
       </c>
-      <c r="C41">
+      <c r="C58">
         <v>2</v>
       </c>
-      <c r="D41" t="s">
-        <v>14</v>
-      </c>
-      <c r="E41">
+      <c r="D58" t="s">
+        <v>14</v>
+      </c>
+      <c r="E58">
         <v>7.0000000000000007E-2</v>
       </c>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
+      <c r="F58">
+        <v>0</v>
+      </c>
+      <c r="G58">
+        <v>11</v>
+      </c>
+      <c r="H58" s="1">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A59" t="s">
         <v>15</v>
       </c>
-      <c r="B42">
+      <c r="B59">
         <v>88</v>
       </c>
-      <c r="C42">
+      <c r="C59">
         <v>12</v>
       </c>
-      <c r="D42" t="s">
-        <v>14</v>
-      </c>
-      <c r="E42">
+      <c r="D59" t="s">
+        <v>14</v>
+      </c>
+      <c r="E59">
         <v>0.01</v>
       </c>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
+      <c r="F59">
+        <v>0</v>
+      </c>
+      <c r="G59">
+        <v>11</v>
+      </c>
+      <c r="H59" s="1">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A60" t="s">
         <v>15</v>
       </c>
-      <c r="B43">
+      <c r="B60">
         <v>88</v>
       </c>
-      <c r="C43">
+      <c r="C60">
+        <v>16</v>
+      </c>
+      <c r="D60" t="s">
+        <v>13</v>
+      </c>
+      <c r="E60">
+        <v>0.01</v>
+      </c>
+      <c r="F60">
+        <v>1</v>
+      </c>
+      <c r="G60">
+        <v>11</v>
+      </c>
+      <c r="H60" s="1">
+        <v>19</v>
+      </c>
+      <c r="I60">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="61" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A61" t="s">
+        <v>15</v>
+      </c>
+      <c r="B61">
+        <v>88</v>
+      </c>
+      <c r="C61">
         <v>24</v>
       </c>
-      <c r="D43" t="s">
-        <v>14</v>
-      </c>
-      <c r="E43">
+      <c r="D61" t="s">
+        <v>14</v>
+      </c>
+      <c r="E61">
         <v>0.01</v>
       </c>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
+      <c r="F61">
+        <v>0</v>
+      </c>
+      <c r="G61">
+        <v>11</v>
+      </c>
+      <c r="H61" s="1">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A62" t="s">
         <v>15</v>
       </c>
-      <c r="B44">
+      <c r="B62">
         <v>88</v>
       </c>
-      <c r="C44">
+      <c r="C62">
         <v>30</v>
       </c>
-      <c r="D44" t="s">
-        <v>14</v>
-      </c>
-      <c r="E44">
+      <c r="D62" t="s">
+        <v>14</v>
+      </c>
+      <c r="E62">
         <v>0.22</v>
       </c>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
-        <v>16</v>
-      </c>
-      <c r="B45">
-        <v>21</v>
-      </c>
-      <c r="C45">
-        <v>2</v>
-      </c>
-      <c r="D45" t="s">
-        <v>14</v>
-      </c>
-      <c r="E45">
-        <v>11.74</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A46" t="s">
-        <v>16</v>
-      </c>
-      <c r="B46">
-        <v>21</v>
-      </c>
-      <c r="C46">
-        <v>7</v>
-      </c>
-      <c r="D46" t="s">
-        <v>14</v>
-      </c>
-      <c r="E46">
-        <v>8.3800000000000008</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A47" t="s">
-        <v>16</v>
-      </c>
-      <c r="B47">
-        <v>21</v>
-      </c>
-      <c r="C47">
-        <v>12</v>
-      </c>
-      <c r="D47" t="s">
-        <v>14</v>
-      </c>
-      <c r="E47">
-        <v>7.32</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A48" t="s">
-        <v>16</v>
-      </c>
-      <c r="B48">
-        <v>21</v>
-      </c>
-      <c r="C48">
-        <v>17</v>
-      </c>
-      <c r="D48" t="s">
-        <v>14</v>
-      </c>
-      <c r="E48">
-        <v>8.3699999999999992</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A49" t="s">
-        <v>16</v>
-      </c>
-      <c r="B49">
-        <v>21</v>
-      </c>
-      <c r="C49">
-        <v>21</v>
-      </c>
-      <c r="D49" t="s">
-        <v>14</v>
-      </c>
-      <c r="E49">
-        <v>5.61</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A50" t="s">
-        <v>16</v>
-      </c>
-      <c r="B50">
-        <v>21</v>
-      </c>
-      <c r="C50">
-        <v>23</v>
-      </c>
-      <c r="D50" t="s">
-        <v>14</v>
-      </c>
-      <c r="E50">
-        <v>10.23</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A51" t="s">
-        <v>16</v>
-      </c>
-      <c r="B51">
-        <v>21</v>
-      </c>
-      <c r="C51">
-        <v>32</v>
-      </c>
-      <c r="D51" t="s">
-        <v>14</v>
-      </c>
-      <c r="E51">
-        <v>7.24</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A52" t="s">
-        <v>16</v>
-      </c>
-      <c r="B52">
-        <v>21</v>
-      </c>
-      <c r="C52">
-        <v>37</v>
-      </c>
-      <c r="D52" t="s">
-        <v>14</v>
-      </c>
-      <c r="E52">
-        <v>6.12</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A53" t="s">
-        <v>16</v>
-      </c>
-      <c r="B53">
-        <v>21</v>
-      </c>
-      <c r="C53">
-        <v>43</v>
-      </c>
-      <c r="D53" t="s">
-        <v>14</v>
-      </c>
-      <c r="E53">
-        <v>11.42</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A54" t="s">
-        <v>16</v>
-      </c>
-      <c r="B54">
-        <v>84</v>
-      </c>
-      <c r="C54">
-        <v>2</v>
-      </c>
-      <c r="D54" t="s">
-        <v>14</v>
-      </c>
-      <c r="E54">
-        <v>4.87</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A55" t="s">
-        <v>16</v>
-      </c>
-      <c r="B55">
-        <v>84</v>
-      </c>
-      <c r="C55">
-        <v>7</v>
-      </c>
-      <c r="D55" t="s">
-        <v>14</v>
-      </c>
-      <c r="E55">
-        <v>10.49</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A56" t="s">
-        <v>16</v>
-      </c>
-      <c r="B56">
-        <v>84</v>
-      </c>
-      <c r="C56">
-        <v>12</v>
-      </c>
-      <c r="D56" t="s">
-        <v>14</v>
-      </c>
-      <c r="E56">
-        <v>13.74</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A57" t="s">
-        <v>16</v>
-      </c>
-      <c r="B57">
-        <v>84</v>
-      </c>
-      <c r="C57">
-        <v>23</v>
-      </c>
-      <c r="D57" t="s">
-        <v>14</v>
-      </c>
-      <c r="E57">
-        <v>7.01</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A58" t="s">
-        <v>16</v>
-      </c>
-      <c r="B58">
-        <v>84</v>
-      </c>
-      <c r="C58">
-        <v>32</v>
-      </c>
-      <c r="D58" t="s">
-        <v>14</v>
-      </c>
-      <c r="E58">
-        <v>2.37</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A59" t="s">
-        <v>16</v>
-      </c>
-      <c r="B59">
-        <v>84</v>
-      </c>
-      <c r="C59">
-        <v>37</v>
-      </c>
-      <c r="D59" t="s">
-        <v>14</v>
-      </c>
-      <c r="E59">
-        <v>8.86</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A60" t="s">
-        <v>16</v>
-      </c>
-      <c r="B60">
-        <v>161</v>
-      </c>
-      <c r="C60">
-        <v>2</v>
-      </c>
-      <c r="D60" t="s">
-        <v>14</v>
-      </c>
-      <c r="E60">
-        <v>3.68</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A61" t="s">
-        <v>16</v>
-      </c>
-      <c r="B61">
-        <v>161</v>
-      </c>
-      <c r="C61">
-        <v>7</v>
-      </c>
-      <c r="D61" t="s">
-        <v>14</v>
-      </c>
-      <c r="E61">
-        <v>1.75</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A62" t="s">
-        <v>16</v>
-      </c>
-      <c r="B62">
-        <v>161</v>
-      </c>
-      <c r="C62">
-        <v>32</v>
-      </c>
-      <c r="D62" t="s">
-        <v>14</v>
-      </c>
-      <c r="E62">
-        <v>0.42</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F62">
+        <v>0</v>
+      </c>
+      <c r="G62">
+        <v>11</v>
+      </c>
+      <c r="H62" s="1">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="63" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
         <v>16</v>
       </c>
       <c r="B63">
-        <v>161</v>
+        <v>21</v>
       </c>
       <c r="C63">
-        <v>37</v>
+        <v>1</v>
       </c>
       <c r="D63" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E63">
-        <v>0.24</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+        <v>7.71</v>
+      </c>
+      <c r="F63">
+        <v>0</v>
+      </c>
+      <c r="G63">
+        <v>11</v>
+      </c>
+      <c r="H63" s="1">
+        <v>14</v>
+      </c>
+      <c r="I63">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="64" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
         <v>16</v>
       </c>
       <c r="B64">
-        <v>194</v>
+        <v>21</v>
       </c>
       <c r="C64">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D64" t="s">
         <v>14</v>
       </c>
       <c r="E64">
-        <v>45.25</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+        <v>11.74</v>
+      </c>
+      <c r="F64">
+        <v>0</v>
+      </c>
+      <c r="G64">
+        <v>11</v>
+      </c>
+      <c r="H64" s="1">
+        <v>22</v>
+      </c>
+      <c r="J64">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="65" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="B65">
         <v>21</v>
       </c>
       <c r="C65">
+        <v>5</v>
+      </c>
+      <c r="D65" t="s">
         <v>2</v>
       </c>
-      <c r="D65" t="s">
-        <v>13</v>
-      </c>
       <c r="E65">
-        <v>0.63</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+        <v>0.24</v>
+      </c>
+      <c r="F65">
+        <v>1</v>
+      </c>
+      <c r="G65">
+        <v>11</v>
+      </c>
+      <c r="H65" s="1"/>
+    </row>
+    <row r="66" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="B66">
         <v>21</v>
       </c>
       <c r="C66">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D66" t="s">
         <v>13</v>
       </c>
       <c r="E66">
-        <v>0.32</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+        <v>3.59</v>
+      </c>
+      <c r="F66">
+        <v>0</v>
+      </c>
+      <c r="G66">
+        <v>14</v>
+      </c>
+      <c r="H66" s="1"/>
+    </row>
+    <row r="67" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="B67">
         <v>21</v>
       </c>
       <c r="C67">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="D67" t="s">
+        <v>14</v>
+      </c>
+      <c r="E67">
+        <v>8.3800000000000008</v>
+      </c>
+      <c r="F67">
+        <v>0</v>
+      </c>
+      <c r="H67" s="1"/>
+      <c r="J67">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="68" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A68" t="s">
+        <v>16</v>
+      </c>
+      <c r="B68">
+        <v>21</v>
+      </c>
+      <c r="C68">
+        <v>8</v>
+      </c>
+      <c r="D68" t="s">
+        <v>2</v>
+      </c>
+      <c r="E68">
+        <v>0.03</v>
+      </c>
+      <c r="F68">
+        <v>1</v>
+      </c>
+      <c r="G68">
+        <v>14</v>
+      </c>
+      <c r="H68" s="1"/>
+    </row>
+    <row r="69" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A69" t="s">
+        <v>16</v>
+      </c>
+      <c r="B69">
+        <v>21</v>
+      </c>
+      <c r="C69" s="3">
+        <v>11</v>
+      </c>
+      <c r="D69" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="E67">
-        <v>1.37</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A68" t="s">
-        <v>11</v>
-      </c>
-      <c r="B68">
-        <v>21</v>
-      </c>
-      <c r="C68">
-        <v>30</v>
-      </c>
-      <c r="D68" t="s">
+      <c r="E69">
+        <v>1.3</v>
+      </c>
+      <c r="F69">
+        <v>1</v>
+      </c>
+      <c r="G69">
+        <v>11</v>
+      </c>
+      <c r="H69" s="1"/>
+    </row>
+    <row r="70" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A70" t="s">
+        <v>16</v>
+      </c>
+      <c r="B70">
+        <v>21</v>
+      </c>
+      <c r="C70">
+        <v>12</v>
+      </c>
+      <c r="D70" t="s">
+        <v>14</v>
+      </c>
+      <c r="E70">
+        <v>7.32</v>
+      </c>
+      <c r="F70">
+        <v>0</v>
+      </c>
+      <c r="H70" s="1"/>
+    </row>
+    <row r="71" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A71" t="s">
+        <v>16</v>
+      </c>
+      <c r="B71">
+        <v>21</v>
+      </c>
+      <c r="C71" s="3">
+        <v>16</v>
+      </c>
+      <c r="D71" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="E68">
-        <v>1.63</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A69" t="s">
-        <v>11</v>
-      </c>
-      <c r="B69">
-        <v>89</v>
-      </c>
-      <c r="C69">
-        <v>2</v>
-      </c>
-      <c r="D69" t="s">
+      <c r="E71">
+        <v>0.19</v>
+      </c>
+      <c r="F71">
+        <v>1</v>
+      </c>
+      <c r="G71">
+        <v>11</v>
+      </c>
+      <c r="H71" s="1"/>
+    </row>
+    <row r="72" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A72" t="s">
+        <v>16</v>
+      </c>
+      <c r="B72">
+        <v>21</v>
+      </c>
+      <c r="C72">
+        <v>17</v>
+      </c>
+      <c r="D72" t="s">
+        <v>14</v>
+      </c>
+      <c r="E72">
+        <v>8.3699999999999992</v>
+      </c>
+      <c r="F72" s="2">
+        <v>1</v>
+      </c>
+      <c r="G72">
+        <v>11</v>
+      </c>
+      <c r="H72" s="1">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="73" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A73" t="s">
+        <v>16</v>
+      </c>
+      <c r="B73">
+        <v>21</v>
+      </c>
+      <c r="C73" s="3">
+        <v>20</v>
+      </c>
+      <c r="D73" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="E69">
-        <v>0.59</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A70" t="s">
-        <v>11</v>
-      </c>
-      <c r="B70">
-        <v>89</v>
-      </c>
-      <c r="C70">
-        <v>10</v>
-      </c>
-      <c r="D70" t="s">
+      <c r="E73">
+        <v>0.63</v>
+      </c>
+      <c r="F73">
+        <v>1</v>
+      </c>
+      <c r="G73">
+        <v>14</v>
+      </c>
+      <c r="H73" s="1"/>
+    </row>
+    <row r="74" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A74" t="s">
+        <v>16</v>
+      </c>
+      <c r="B74">
+        <v>21</v>
+      </c>
+      <c r="C74">
+        <v>21</v>
+      </c>
+      <c r="D74" t="s">
+        <v>14</v>
+      </c>
+      <c r="E74">
+        <v>5.61</v>
+      </c>
+      <c r="F74">
+        <v>1</v>
+      </c>
+      <c r="G74">
+        <v>11</v>
+      </c>
+      <c r="H74" s="1"/>
+    </row>
+    <row r="75" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A75" t="s">
+        <v>16</v>
+      </c>
+      <c r="B75">
+        <v>21</v>
+      </c>
+      <c r="C75">
+        <v>23</v>
+      </c>
+      <c r="D75" t="s">
+        <v>14</v>
+      </c>
+      <c r="E75">
+        <v>10.23</v>
+      </c>
+      <c r="F75">
+        <v>0</v>
+      </c>
+      <c r="G75">
+        <v>55</v>
+      </c>
+      <c r="H75" s="1"/>
+    </row>
+    <row r="76" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A76" t="s">
+        <v>16</v>
+      </c>
+      <c r="B76">
+        <v>21</v>
+      </c>
+      <c r="C76" s="3">
+        <v>26</v>
+      </c>
+      <c r="D76" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="E70">
-        <v>0.36</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A71" t="s">
-        <v>11</v>
-      </c>
-      <c r="B71">
-        <v>89</v>
-      </c>
-      <c r="C71">
-        <v>30</v>
-      </c>
-      <c r="D71" t="s">
+      <c r="E76">
+        <v>2.11</v>
+      </c>
+      <c r="F76">
+        <v>1</v>
+      </c>
+      <c r="G76">
+        <v>11</v>
+      </c>
+      <c r="H76" s="1"/>
+    </row>
+    <row r="77" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A77" t="s">
+        <v>16</v>
+      </c>
+      <c r="B77">
+        <v>21</v>
+      </c>
+      <c r="C77" s="3">
+        <v>28</v>
+      </c>
+      <c r="D77" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="E71">
-        <v>13.8</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A72" t="s">
-        <v>15</v>
-      </c>
-      <c r="B72">
-        <v>25</v>
-      </c>
-      <c r="C72">
-        <v>11</v>
-      </c>
-      <c r="D72" t="s">
-        <v>13</v>
-      </c>
-      <c r="E72">
-        <v>9.9600000000000009</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A73" t="s">
-        <v>15</v>
-      </c>
-      <c r="B73">
-        <v>25</v>
-      </c>
-      <c r="C73">
-        <v>16</v>
-      </c>
-      <c r="D73" t="s">
-        <v>13</v>
-      </c>
-      <c r="E73">
-        <v>11.14</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A74" t="s">
-        <v>15</v>
-      </c>
-      <c r="B74">
-        <v>25</v>
-      </c>
-      <c r="C74">
-        <v>23</v>
-      </c>
-      <c r="D74" t="s">
-        <v>13</v>
-      </c>
-      <c r="E74">
-        <v>7.73</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A75" t="s">
-        <v>15</v>
-      </c>
-      <c r="B75">
-        <v>25</v>
-      </c>
-      <c r="C75">
-        <v>29</v>
-      </c>
-      <c r="D75" t="s">
-        <v>13</v>
-      </c>
-      <c r="E75">
-        <v>13.1</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A76" t="s">
-        <v>15</v>
-      </c>
-      <c r="B76">
-        <v>25</v>
-      </c>
-      <c r="C76">
-        <v>36</v>
-      </c>
-      <c r="D76" t="s">
-        <v>13</v>
-      </c>
-      <c r="E76">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A77" t="s">
-        <v>15</v>
-      </c>
-      <c r="B77">
-        <v>88</v>
-      </c>
-      <c r="C77">
-        <v>16</v>
-      </c>
-      <c r="D77" t="s">
-        <v>13</v>
-      </c>
       <c r="E77">
-        <v>0.01</v>
-      </c>
-    </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
+        <v>4.01</v>
+      </c>
+      <c r="F77">
+        <v>0</v>
+      </c>
+      <c r="G77">
+        <v>14</v>
+      </c>
+      <c r="H77" s="1"/>
+      <c r="J77">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="78" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
         <v>16</v>
       </c>
@@ -2301,16 +2915,23 @@
         <v>21</v>
       </c>
       <c r="C78">
-        <v>1</v>
+        <v>32</v>
       </c>
       <c r="D78" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E78">
-        <v>7.71</v>
-      </c>
-    </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
+        <v>7.24</v>
+      </c>
+      <c r="F78">
+        <v>0</v>
+      </c>
+      <c r="H78" s="1"/>
+      <c r="J78">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="79" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
         <v>16</v>
       </c>
@@ -2318,33 +2939,52 @@
         <v>21</v>
       </c>
       <c r="C79">
-        <v>6</v>
+        <v>35</v>
       </c>
       <c r="D79" t="s">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="E79">
-        <v>3.59</v>
-      </c>
-    </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+      <c r="F79">
+        <v>1</v>
+      </c>
+      <c r="G79">
+        <v>11</v>
+      </c>
+      <c r="H79" s="1"/>
+    </row>
+    <row r="80" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
         <v>16</v>
       </c>
       <c r="B80">
         <v>21</v>
       </c>
-      <c r="C80">
-        <v>11</v>
-      </c>
-      <c r="D80" t="s">
+      <c r="C80" s="3">
+        <v>36</v>
+      </c>
+      <c r="D80" s="3" t="s">
         <v>13</v>
       </c>
       <c r="E80">
-        <v>1.3</v>
-      </c>
-    </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
+        <v>6.77</v>
+      </c>
+      <c r="F80">
+        <v>0</v>
+      </c>
+      <c r="G80">
+        <v>11</v>
+      </c>
+      <c r="H80" s="1">
+        <v>22</v>
+      </c>
+      <c r="I80">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="81" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
         <v>16</v>
       </c>
@@ -2352,16 +2992,28 @@
         <v>21</v>
       </c>
       <c r="C81">
-        <v>16</v>
+        <v>37</v>
       </c>
       <c r="D81" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E81">
-        <v>0.19</v>
-      </c>
-    </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
+        <v>6.12</v>
+      </c>
+      <c r="F81">
+        <v>0</v>
+      </c>
+      <c r="G81">
+        <v>11</v>
+      </c>
+      <c r="H81" s="1">
+        <v>22</v>
+      </c>
+      <c r="I81">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="82" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
         <v>16</v>
       </c>
@@ -2369,16 +3021,23 @@
         <v>21</v>
       </c>
       <c r="C82">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="D82" t="s">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="E82">
-        <v>0.63</v>
-      </c>
-    </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
+        <v>0.01</v>
+      </c>
+      <c r="F82">
+        <v>1</v>
+      </c>
+      <c r="G82">
+        <v>11</v>
+      </c>
+      <c r="H82" s="1"/>
+    </row>
+    <row r="83" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
         <v>16</v>
       </c>
@@ -2386,16 +3045,23 @@
         <v>21</v>
       </c>
       <c r="C83">
-        <v>26</v>
+        <v>41</v>
       </c>
       <c r="D83" t="s">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="E83">
-        <v>2.11</v>
-      </c>
-    </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+      <c r="F83">
+        <v>1</v>
+      </c>
+      <c r="G83">
+        <v>11</v>
+      </c>
+      <c r="H83" s="1"/>
+    </row>
+    <row r="84" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
         <v>16</v>
       </c>
@@ -2403,33 +3069,54 @@
         <v>21</v>
       </c>
       <c r="C84">
-        <v>28</v>
+        <v>43</v>
       </c>
       <c r="D84" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E84">
-        <v>4.01</v>
-      </c>
-    </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
+        <v>11.42</v>
+      </c>
+      <c r="F84">
+        <v>0</v>
+      </c>
+      <c r="G84">
+        <v>14</v>
+      </c>
+      <c r="H84" s="1">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="85" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
         <v>16</v>
       </c>
       <c r="B85">
-        <v>21</v>
+        <v>84</v>
       </c>
       <c r="C85">
-        <v>36</v>
+        <v>2</v>
       </c>
       <c r="D85" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E85">
-        <v>6.77</v>
-      </c>
-    </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
+        <v>4.87</v>
+      </c>
+      <c r="F85">
+        <v>0</v>
+      </c>
+      <c r="G85">
+        <v>11</v>
+      </c>
+      <c r="H85" s="1">
+        <v>22</v>
+      </c>
+      <c r="J85">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="86" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
         <v>16</v>
       </c>
@@ -2437,16 +3124,23 @@
         <v>84</v>
       </c>
       <c r="C86">
-        <v>28</v>
+        <v>7</v>
       </c>
       <c r="D86" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E86">
-        <v>1.58</v>
-      </c>
-    </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
+        <v>10.49</v>
+      </c>
+      <c r="F86">
+        <v>0</v>
+      </c>
+      <c r="H86" s="1"/>
+      <c r="J86">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="87" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
         <v>16</v>
       </c>
@@ -2454,205 +3148,1382 @@
         <v>84</v>
       </c>
       <c r="C87">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="D87" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E87">
-        <v>33.82</v>
-      </c>
-    </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
+        <v>13.74</v>
+      </c>
+      <c r="F87">
+        <v>0</v>
+      </c>
+      <c r="H87" s="1"/>
+    </row>
+    <row r="88" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
         <v>16</v>
       </c>
       <c r="B88">
+        <v>84</v>
+      </c>
+      <c r="C88">
+        <v>23</v>
+      </c>
+      <c r="D88" t="s">
+        <v>14</v>
+      </c>
+      <c r="E88">
+        <v>7.01</v>
+      </c>
+      <c r="F88">
+        <v>1</v>
+      </c>
+      <c r="G88">
+        <v>55</v>
+      </c>
+      <c r="H88" s="1"/>
+    </row>
+    <row r="89" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A89" t="s">
+        <v>16</v>
+      </c>
+      <c r="B89">
+        <v>84</v>
+      </c>
+      <c r="C89" s="3">
+        <v>28</v>
+      </c>
+      <c r="D89" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E89">
+        <v>1.58</v>
+      </c>
+      <c r="F89">
+        <v>0</v>
+      </c>
+      <c r="G89">
+        <v>14</v>
+      </c>
+      <c r="H89" s="1"/>
+      <c r="J89">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="90" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A90" t="s">
+        <v>16</v>
+      </c>
+      <c r="B90">
+        <v>84</v>
+      </c>
+      <c r="C90">
+        <v>32</v>
+      </c>
+      <c r="D90" t="s">
+        <v>14</v>
+      </c>
+      <c r="E90">
+        <v>2.37</v>
+      </c>
+      <c r="F90">
+        <v>0</v>
+      </c>
+      <c r="H90" s="1"/>
+      <c r="J90">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="91" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A91" t="s">
+        <v>16</v>
+      </c>
+      <c r="B91">
+        <v>84</v>
+      </c>
+      <c r="C91" s="3">
+        <v>36</v>
+      </c>
+      <c r="D91" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E91">
+        <v>33.82</v>
+      </c>
+      <c r="F91">
+        <v>1</v>
+      </c>
+      <c r="G91">
+        <v>11</v>
+      </c>
+      <c r="H91" s="1">
+        <v>22</v>
+      </c>
+      <c r="I91">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="92" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A92" t="s">
+        <v>16</v>
+      </c>
+      <c r="B92">
+        <v>84</v>
+      </c>
+      <c r="C92">
+        <v>37</v>
+      </c>
+      <c r="D92" t="s">
+        <v>14</v>
+      </c>
+      <c r="E92">
+        <v>8.86</v>
+      </c>
+      <c r="F92">
+        <v>0</v>
+      </c>
+      <c r="G92">
+        <v>11</v>
+      </c>
+      <c r="H92" s="1">
+        <v>22</v>
+      </c>
+      <c r="I92">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="93" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A93" t="s">
+        <v>16</v>
+      </c>
+      <c r="B93">
         <v>161</v>
       </c>
-      <c r="C88">
+      <c r="C93">
+        <v>2</v>
+      </c>
+      <c r="D93" t="s">
+        <v>14</v>
+      </c>
+      <c r="E93">
+        <v>3.68</v>
+      </c>
+      <c r="F93">
+        <v>1</v>
+      </c>
+      <c r="G93">
+        <v>11</v>
+      </c>
+      <c r="H93" s="1">
+        <v>22</v>
+      </c>
+      <c r="J93">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="94" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A94" t="s">
+        <v>16</v>
+      </c>
+      <c r="B94">
+        <v>161</v>
+      </c>
+      <c r="C94">
+        <v>7</v>
+      </c>
+      <c r="D94" t="s">
+        <v>14</v>
+      </c>
+      <c r="E94">
+        <v>1.75</v>
+      </c>
+      <c r="F94">
+        <v>0</v>
+      </c>
+      <c r="H94" s="1"/>
+      <c r="J94">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="95" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A95" t="s">
+        <v>16</v>
+      </c>
+      <c r="B95">
+        <v>161</v>
+      </c>
+      <c r="C95" s="3">
         <v>28</v>
       </c>
-      <c r="D88" t="s">
+      <c r="D95" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="E88">
+      <c r="E95">
         <v>0.18</v>
       </c>
-    </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A89" t="s">
-        <v>11</v>
-      </c>
-      <c r="B89">
-        <v>21</v>
-      </c>
-      <c r="C89">
-        <v>1</v>
-      </c>
-      <c r="D89" t="s">
+      <c r="F95">
+        <v>1</v>
+      </c>
+      <c r="G95">
+        <v>14</v>
+      </c>
+      <c r="H95" s="1"/>
+      <c r="J95">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="96" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A96" t="s">
+        <v>16</v>
+      </c>
+      <c r="B96">
+        <v>161</v>
+      </c>
+      <c r="C96">
+        <v>32</v>
+      </c>
+      <c r="D96" t="s">
+        <v>14</v>
+      </c>
+      <c r="E96">
+        <v>0.42</v>
+      </c>
+      <c r="F96">
+        <v>1</v>
+      </c>
+      <c r="H96" s="1"/>
+      <c r="J96">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="97" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A97" t="s">
+        <v>16</v>
+      </c>
+      <c r="B97">
+        <v>161</v>
+      </c>
+      <c r="C97">
+        <v>37</v>
+      </c>
+      <c r="D97" t="s">
+        <v>14</v>
+      </c>
+      <c r="E97">
+        <v>0.24</v>
+      </c>
+      <c r="F97">
+        <v>1</v>
+      </c>
+      <c r="G97">
+        <v>11</v>
+      </c>
+      <c r="H97" s="1">
+        <v>22</v>
+      </c>
+      <c r="I97">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="98" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A98" t="s">
+        <v>16</v>
+      </c>
+      <c r="B98">
+        <v>194</v>
+      </c>
+      <c r="C98">
+        <v>7</v>
+      </c>
+      <c r="D98" t="s">
+        <v>14</v>
+      </c>
+      <c r="E98">
+        <v>45.25</v>
+      </c>
+      <c r="F98">
+        <v>1</v>
+      </c>
+      <c r="H98" s="1"/>
+    </row>
+    <row r="99" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A99" t="s">
+        <v>23</v>
+      </c>
+      <c r="B99">
+        <v>26</v>
+      </c>
+      <c r="C99">
+        <v>1</v>
+      </c>
+      <c r="D99" t="s">
+        <v>2</v>
+      </c>
+      <c r="E99">
+        <v>1.0577657636481166</v>
+      </c>
+    </row>
+    <row r="100" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A100" t="s">
+        <v>23</v>
+      </c>
+      <c r="B100">
+        <v>26</v>
+      </c>
+      <c r="C100">
+        <v>2</v>
+      </c>
+      <c r="D100" t="s">
+        <v>2</v>
+      </c>
+      <c r="E100">
+        <v>0.17460640805517563</v>
+      </c>
+    </row>
+    <row r="101" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A101" t="s">
+        <v>23</v>
+      </c>
+      <c r="B101">
+        <v>26</v>
+      </c>
+      <c r="C101">
+        <v>3</v>
+      </c>
+      <c r="D101" t="s">
+        <v>24</v>
+      </c>
+      <c r="E101">
+        <v>19.991828952744111</v>
+      </c>
+    </row>
+    <row r="102" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A102" t="s">
+        <v>23</v>
+      </c>
+      <c r="B102">
+        <v>26</v>
+      </c>
+      <c r="C102">
+        <v>4</v>
+      </c>
+      <c r="D102" t="s">
+        <v>24</v>
+      </c>
+      <c r="E102">
+        <v>2.6998689384010488</v>
+      </c>
+    </row>
+    <row r="103" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A103" t="s">
+        <v>23</v>
+      </c>
+      <c r="B103">
+        <v>26</v>
+      </c>
+      <c r="C103">
+        <v>5</v>
+      </c>
+      <c r="D103" t="s">
+        <v>25</v>
+      </c>
+      <c r="E103">
+        <v>211.32042560613991</v>
+      </c>
+    </row>
+    <row r="104" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A104" t="s">
+        <v>23</v>
+      </c>
+      <c r="B104">
+        <v>26</v>
+      </c>
+      <c r="C104">
+        <v>6</v>
+      </c>
+      <c r="D104" t="s">
+        <v>25</v>
+      </c>
+      <c r="E104">
+        <v>41.197975253093361</v>
+      </c>
+    </row>
+    <row r="105" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A105" t="s">
+        <v>23</v>
+      </c>
+      <c r="B105">
+        <v>26</v>
+      </c>
+      <c r="C105">
+        <v>7</v>
+      </c>
+      <c r="D105" t="s">
+        <v>2</v>
+      </c>
+      <c r="E105">
+        <v>0.12223071046600459</v>
+      </c>
+    </row>
+    <row r="106" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A106" t="s">
+        <v>23</v>
+      </c>
+      <c r="B106">
+        <v>26</v>
+      </c>
+      <c r="C106">
+        <v>8</v>
+      </c>
+      <c r="D106" t="s">
+        <v>2</v>
+      </c>
+      <c r="E106">
+        <v>0.52889433247967932</v>
+      </c>
+    </row>
+    <row r="107" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A107" t="s">
+        <v>23</v>
+      </c>
+      <c r="B107">
+        <v>26</v>
+      </c>
+      <c r="C107">
+        <v>9</v>
+      </c>
+      <c r="D107" t="s">
+        <v>24</v>
+      </c>
+      <c r="E107">
+        <v>3.4331895242146198</v>
+      </c>
+    </row>
+    <row r="108" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A108" t="s">
+        <v>23</v>
+      </c>
+      <c r="B108">
+        <v>26</v>
+      </c>
+      <c r="C108">
+        <v>10</v>
+      </c>
+      <c r="D108" t="s">
+        <v>24</v>
+      </c>
+      <c r="E108">
+        <v>5.0114458949452452</v>
+      </c>
+    </row>
+    <row r="109" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A109" t="s">
+        <v>23</v>
+      </c>
+      <c r="B109">
+        <v>26</v>
+      </c>
+      <c r="C109">
+        <v>11</v>
+      </c>
+      <c r="D109" t="s">
+        <v>25</v>
+      </c>
+      <c r="E109">
+        <v>43.878424657534246</v>
+      </c>
+    </row>
+    <row r="110" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A110" t="s">
+        <v>23</v>
+      </c>
+      <c r="B110">
+        <v>26</v>
+      </c>
+      <c r="C110">
         <v>12</v>
       </c>
-      <c r="E89">
-        <v>0.05</v>
-      </c>
-    </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A90" t="s">
-        <v>11</v>
-      </c>
-      <c r="B90">
-        <v>21</v>
-      </c>
-      <c r="C90">
-        <v>14</v>
-      </c>
-      <c r="D90" t="s">
+      <c r="D110" t="s">
+        <v>25</v>
+      </c>
+      <c r="E110">
+        <v>47.487810048759798</v>
+      </c>
+    </row>
+    <row r="111" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A111" t="s">
+        <v>23</v>
+      </c>
+      <c r="B111">
+        <v>26</v>
+      </c>
+      <c r="C111">
+        <v>14</v>
+      </c>
+      <c r="D111" t="s">
+        <v>24</v>
+      </c>
+      <c r="E111">
+        <v>9.0045298862004195</v>
+      </c>
+    </row>
+    <row r="112" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A112" t="s">
+        <v>23</v>
+      </c>
+      <c r="B112">
+        <v>26</v>
+      </c>
+      <c r="C112">
+        <v>15</v>
+      </c>
+      <c r="D112" t="s">
+        <v>25</v>
+      </c>
+      <c r="E112">
+        <v>20.851735860167562</v>
+      </c>
+    </row>
+    <row r="113" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A113" t="s">
+        <v>23</v>
+      </c>
+      <c r="B113">
+        <v>26</v>
+      </c>
+      <c r="C113">
+        <v>16</v>
+      </c>
+      <c r="D113" t="s">
+        <v>2</v>
+      </c>
+      <c r="E113">
+        <v>0.36572328813368588</v>
+      </c>
+    </row>
+    <row r="114" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A114" t="s">
+        <v>23</v>
+      </c>
+      <c r="B114">
+        <v>26</v>
+      </c>
+      <c r="C114">
+        <v>17</v>
+      </c>
+      <c r="D114" t="s">
+        <v>2</v>
+      </c>
+      <c r="E114">
+        <v>0.61462814996926873</v>
+      </c>
+    </row>
+    <row r="115" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A115" t="s">
+        <v>23</v>
+      </c>
+      <c r="B115">
+        <v>26</v>
+      </c>
+      <c r="C115">
+        <v>18</v>
+      </c>
+      <c r="D115" t="s">
+        <v>24</v>
+      </c>
+      <c r="E115">
+        <v>17.784426161389511</v>
+      </c>
+    </row>
+    <row r="116" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A116" t="s">
+        <v>23</v>
+      </c>
+      <c r="B116">
+        <v>26</v>
+      </c>
+      <c r="C116">
+        <v>19</v>
+      </c>
+      <c r="D116" t="s">
+        <v>25</v>
+      </c>
+      <c r="E116">
+        <v>21.577227635336023</v>
+      </c>
+    </row>
+    <row r="117" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A117" t="s">
+        <v>23</v>
+      </c>
+      <c r="B117">
+        <v>26</v>
+      </c>
+      <c r="C117">
+        <v>20</v>
+      </c>
+      <c r="D117" t="s">
+        <v>2</v>
+      </c>
+      <c r="E117">
+        <v>0.25822741227440965</v>
+      </c>
+    </row>
+    <row r="118" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A118" t="s">
+        <v>23</v>
+      </c>
+      <c r="B118">
+        <v>26</v>
+      </c>
+      <c r="C118">
+        <v>21</v>
+      </c>
+      <c r="D118" t="s">
+        <v>2</v>
+      </c>
+      <c r="E118">
+        <v>0.77259850630955451</v>
+      </c>
+    </row>
+    <row r="119" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A119" t="s">
+        <v>23</v>
+      </c>
+      <c r="B119">
+        <v>26</v>
+      </c>
+      <c r="C119">
+        <v>22</v>
+      </c>
+      <c r="D119" t="s">
+        <v>24</v>
+      </c>
+      <c r="E119">
+        <v>4.7538082515007467</v>
+      </c>
+    </row>
+    <row r="120" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A120" t="s">
+        <v>23</v>
+      </c>
+      <c r="B120">
+        <v>26</v>
+      </c>
+      <c r="C120">
+        <v>23</v>
+      </c>
+      <c r="D120" t="s">
+        <v>24</v>
+      </c>
+      <c r="E120">
+        <v>5.8993923979087182</v>
+      </c>
+    </row>
+    <row r="121" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A121" t="s">
+        <v>23</v>
+      </c>
+      <c r="B121">
+        <v>26</v>
+      </c>
+      <c r="C121">
+        <v>24</v>
+      </c>
+      <c r="D121" t="s">
+        <v>25</v>
+      </c>
+      <c r="E121">
+        <v>117.60964548420995</v>
+      </c>
+    </row>
+    <row r="122" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A122" t="s">
+        <v>23</v>
+      </c>
+      <c r="B122">
+        <v>26</v>
+      </c>
+      <c r="C122">
+        <v>25</v>
+      </c>
+      <c r="D122" t="s">
+        <v>25</v>
+      </c>
+      <c r="E122">
+        <v>31.239992883828506</v>
+      </c>
+    </row>
+    <row r="123" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A123" t="s">
+        <v>26</v>
+      </c>
+      <c r="B123">
+        <v>27</v>
+      </c>
+      <c r="C123">
+        <v>2</v>
+      </c>
+      <c r="D123" t="s">
+        <v>2</v>
+      </c>
+      <c r="E123">
+        <v>0.2763957987838585</v>
+      </c>
+    </row>
+    <row r="124" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A124" t="s">
+        <v>26</v>
+      </c>
+      <c r="B124">
+        <v>27</v>
+      </c>
+      <c r="C124">
+        <v>3</v>
+      </c>
+      <c r="D124" t="s">
+        <v>24</v>
+      </c>
+      <c r="E124">
+        <v>6.1667488899851994</v>
+      </c>
+    </row>
+    <row r="125" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A125" t="s">
+        <v>26</v>
+      </c>
+      <c r="B125">
+        <v>27</v>
+      </c>
+      <c r="C125">
+        <v>4</v>
+      </c>
+      <c r="D125" t="s">
+        <v>2</v>
+      </c>
+      <c r="E125">
+        <v>0.18428424001179419</v>
+      </c>
+    </row>
+    <row r="126" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A126" t="s">
+        <v>26</v>
+      </c>
+      <c r="B126">
+        <v>27</v>
+      </c>
+      <c r="C126">
+        <v>5</v>
+      </c>
+      <c r="D126" t="s">
+        <v>24</v>
+      </c>
+      <c r="E126">
+        <v>6.6952914635033842</v>
+      </c>
+    </row>
+    <row r="127" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A127" t="s">
+        <v>26</v>
+      </c>
+      <c r="B127">
+        <v>27</v>
+      </c>
+      <c r="C127">
+        <v>6</v>
+      </c>
+      <c r="D127" t="s">
+        <v>25</v>
+      </c>
+      <c r="E127">
+        <v>174.50812660393498</v>
+      </c>
+    </row>
+    <row r="128" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A128" t="s">
+        <v>26</v>
+      </c>
+      <c r="B128">
+        <v>27</v>
+      </c>
+      <c r="C128">
+        <v>7</v>
+      </c>
+      <c r="D128" t="s">
+        <v>2</v>
+      </c>
+      <c r="E128">
+        <v>0.74211502782931349</v>
+      </c>
+    </row>
+    <row r="129" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A129" t="s">
+        <v>26</v>
+      </c>
+      <c r="B129">
+        <v>27</v>
+      </c>
+      <c r="C129">
+        <v>9</v>
+      </c>
+      <c r="D129" t="s">
+        <v>24</v>
+      </c>
+      <c r="E129">
+        <v>15.261446084563422</v>
+      </c>
+    </row>
+    <row r="130" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A130" t="s">
+        <v>26</v>
+      </c>
+      <c r="B130">
+        <v>27</v>
+      </c>
+      <c r="C130">
+        <v>10</v>
+      </c>
+      <c r="D130" t="s">
+        <v>24</v>
+      </c>
+      <c r="E130">
+        <v>8.3014048531289912</v>
+      </c>
+    </row>
+    <row r="131" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A131" t="s">
+        <v>26</v>
+      </c>
+      <c r="B131">
+        <v>27</v>
+      </c>
+      <c r="C131">
+        <v>11</v>
+      </c>
+      <c r="D131" t="s">
+        <v>25</v>
+      </c>
+      <c r="E131">
+        <v>104.56226880394576</v>
+      </c>
+    </row>
+    <row r="132" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A132" t="s">
+        <v>26</v>
+      </c>
+      <c r="B132">
+        <v>27</v>
+      </c>
+      <c r="C132">
         <v>12</v>
       </c>
-      <c r="E90">
-        <v>0.02</v>
-      </c>
-    </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A91" t="s">
-        <v>11</v>
-      </c>
-      <c r="B91">
-        <v>21</v>
-      </c>
-      <c r="C91">
+      <c r="D132" t="s">
+        <v>25</v>
+      </c>
+      <c r="E132">
+        <v>23.433301085671289</v>
+      </c>
+    </row>
+    <row r="133" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A133" t="s">
+        <v>26</v>
+      </c>
+      <c r="B133">
+        <v>27</v>
+      </c>
+      <c r="C133">
+        <v>13</v>
+      </c>
+      <c r="D133" t="s">
+        <v>2</v>
+      </c>
+      <c r="E133">
+        <v>1.0822510822510825</v>
+      </c>
+    </row>
+    <row r="134" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A134" t="s">
+        <v>26</v>
+      </c>
+      <c r="B134">
+        <v>27</v>
+      </c>
+      <c r="C134">
+        <v>14</v>
+      </c>
+      <c r="D134" t="s">
+        <v>25</v>
+      </c>
+      <c r="E134">
+        <v>31.99327498392919</v>
+      </c>
+    </row>
+    <row r="135" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A135" t="s">
+        <v>26</v>
+      </c>
+      <c r="B135">
+        <v>27</v>
+      </c>
+      <c r="C135">
+        <v>15</v>
+      </c>
+      <c r="D135" t="s">
+        <v>2</v>
+      </c>
+      <c r="E135">
+        <v>4.4904661371937928</v>
+      </c>
+    </row>
+    <row r="136" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A136" t="s">
+        <v>26</v>
+      </c>
+      <c r="B136">
+        <v>27</v>
+      </c>
+      <c r="C136">
+        <v>16</v>
+      </c>
+      <c r="D136" t="s">
+        <v>24</v>
+      </c>
+      <c r="E136">
+        <v>10.916747651441529</v>
+      </c>
+    </row>
+    <row r="137" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A137" t="s">
+        <v>26</v>
+      </c>
+      <c r="B137">
+        <v>27</v>
+      </c>
+      <c r="C137">
         <v>17</v>
       </c>
-      <c r="D91" t="s">
-        <v>12</v>
-      </c>
-      <c r="E91">
-        <v>0.05</v>
-      </c>
-    </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A92" t="s">
-        <v>11</v>
-      </c>
-      <c r="B92">
-        <v>21</v>
-      </c>
-      <c r="C92">
+      <c r="D137" t="s">
+        <v>24</v>
+      </c>
+      <c r="E137">
+        <v>35.679978043090436</v>
+      </c>
+    </row>
+    <row r="138" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A138" t="s">
+        <v>26</v>
+      </c>
+      <c r="B138">
+        <v>27</v>
+      </c>
+      <c r="C138">
+        <v>18</v>
+      </c>
+      <c r="D138" t="s">
+        <v>25</v>
+      </c>
+      <c r="E138">
+        <v>198.10997218305835</v>
+      </c>
+    </row>
+    <row r="139" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A139" t="s">
+        <v>26</v>
+      </c>
+      <c r="B139">
+        <v>27</v>
+      </c>
+      <c r="C139">
+        <v>19</v>
+      </c>
+      <c r="D139" t="s">
+        <v>25</v>
+      </c>
+      <c r="E139">
+        <v>120.27829739752552</v>
+      </c>
+    </row>
+    <row r="140" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A140" t="s">
+        <v>26</v>
+      </c>
+      <c r="B140">
+        <v>27</v>
+      </c>
+      <c r="C140">
+        <v>20</v>
+      </c>
+      <c r="D140" t="s">
+        <v>2</v>
+      </c>
+      <c r="E140">
+        <v>0.42121634319411594</v>
+      </c>
+    </row>
+    <row r="141" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A141" t="s">
+        <v>26</v>
+      </c>
+      <c r="B141">
+        <v>27</v>
+      </c>
+      <c r="C141">
+        <v>21</v>
+      </c>
+      <c r="D141" t="s">
+        <v>24</v>
+      </c>
+      <c r="E141">
+        <v>21.348717447280077</v>
+      </c>
+    </row>
+    <row r="142" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A142" t="s">
+        <v>26</v>
+      </c>
+      <c r="B142">
+        <v>27</v>
+      </c>
+      <c r="C142">
+        <v>22</v>
+      </c>
+      <c r="D142" t="s">
+        <v>24</v>
+      </c>
+      <c r="E142">
+        <v>7.5543545019039424</v>
+      </c>
+    </row>
+    <row r="143" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A143" t="s">
+        <v>26</v>
+      </c>
+      <c r="B143">
+        <v>27</v>
+      </c>
+      <c r="C143">
+        <v>23</v>
+      </c>
+      <c r="D143" t="s">
+        <v>25</v>
+      </c>
+      <c r="E143">
+        <v>98.704866562009414</v>
+      </c>
+    </row>
+    <row r="144" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A144" t="s">
+        <v>26</v>
+      </c>
+      <c r="B144">
+        <v>27</v>
+      </c>
+      <c r="C144">
+        <v>24</v>
+      </c>
+      <c r="D144" t="s">
+        <v>27</v>
+      </c>
+      <c r="E144">
+        <v>0.24154589371980678</v>
+      </c>
+    </row>
+    <row r="145" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A145" t="s">
+        <v>26</v>
+      </c>
+      <c r="B145">
+        <v>27</v>
+      </c>
+      <c r="C145">
+        <v>25</v>
+      </c>
+      <c r="D145" t="s">
+        <v>27</v>
+      </c>
+      <c r="E145">
+        <v>0.64090239056591669</v>
+      </c>
+    </row>
+    <row r="146" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A146" t="s">
+        <v>26</v>
+      </c>
+      <c r="B146">
+        <v>27</v>
+      </c>
+      <c r="C146">
+        <v>26</v>
+      </c>
+      <c r="D146" t="s">
+        <v>27</v>
+      </c>
+      <c r="E146">
+        <v>0.21715526601520088</v>
+      </c>
+    </row>
+    <row r="147" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A147" t="s">
+        <v>26</v>
+      </c>
+      <c r="B147">
+        <v>27</v>
+      </c>
+      <c r="C147">
+        <v>27</v>
+      </c>
+      <c r="D147" t="s">
+        <v>28</v>
+      </c>
+      <c r="E147">
+        <v>1.4043150772373292</v>
+      </c>
+    </row>
+    <row r="148" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A148" t="s">
+        <v>26</v>
+      </c>
+      <c r="B148">
+        <v>27</v>
+      </c>
+      <c r="C148">
+        <v>28</v>
+      </c>
+      <c r="D148" t="s">
+        <v>28</v>
+      </c>
+      <c r="E148">
+        <v>3.3067378575979127</v>
+      </c>
+    </row>
+    <row r="149" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A149" t="s">
+        <v>26</v>
+      </c>
+      <c r="B149">
+        <v>27</v>
+      </c>
+      <c r="C149">
+        <v>29</v>
+      </c>
+      <c r="D149" t="s">
+        <v>28</v>
+      </c>
+      <c r="E149">
+        <v>0.30388671103412646</v>
+      </c>
+    </row>
+    <row r="150" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A150" t="s">
+        <v>26</v>
+      </c>
+      <c r="B150">
+        <v>27</v>
+      </c>
+      <c r="C150">
+        <v>30</v>
+      </c>
+      <c r="D150" t="s">
+        <v>24</v>
+      </c>
+      <c r="E150">
+        <v>15.60758082497213</v>
+      </c>
+    </row>
+    <row r="151" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A151" t="s">
+        <v>26</v>
+      </c>
+      <c r="B151">
+        <v>27</v>
+      </c>
+      <c r="C151">
         <v>31</v>
       </c>
-      <c r="D92" t="s">
-        <v>12</v>
-      </c>
-      <c r="E92">
-        <v>0.02</v>
-      </c>
-    </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A93" t="s">
-        <v>15</v>
-      </c>
-      <c r="B93">
+      <c r="D151" t="s">
+        <v>24</v>
+      </c>
+      <c r="E151">
+        <v>50.821000810494404</v>
+      </c>
+    </row>
+    <row r="152" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A152" t="s">
+        <v>26</v>
+      </c>
+      <c r="B152">
+        <v>27</v>
+      </c>
+      <c r="C152">
+        <v>32</v>
+      </c>
+      <c r="D152" t="s">
         <v>25</v>
       </c>
-      <c r="C93">
-        <v>9</v>
-      </c>
-      <c r="D93" t="s">
-        <v>12</v>
-      </c>
-      <c r="E93">
-        <v>0.22</v>
-      </c>
-    </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A94" t="s">
-        <v>15</v>
-      </c>
-      <c r="B94">
+      <c r="E152">
+        <v>78.636660143509459</v>
+      </c>
+    </row>
+    <row r="153" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A153" t="s">
+        <v>26</v>
+      </c>
+      <c r="B153">
+        <v>27</v>
+      </c>
+      <c r="C153">
+        <v>33</v>
+      </c>
+      <c r="D153" t="s">
         <v>25</v>
       </c>
-      <c r="C94">
+      <c r="E153">
+        <v>143.13526324699509</v>
+      </c>
+    </row>
+    <row r="154" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A154" t="s">
+        <v>26</v>
+      </c>
+      <c r="B154">
+        <v>27</v>
+      </c>
+      <c r="C154">
+        <v>34</v>
+      </c>
+      <c r="D154" t="s">
+        <v>25</v>
+      </c>
+      <c r="E154">
+        <v>53.602376825947019</v>
+      </c>
+    </row>
+    <row r="155" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A155" t="s">
+        <v>26</v>
+      </c>
+      <c r="B155">
+        <v>27</v>
+      </c>
+      <c r="C155">
         <v>35</v>
       </c>
-      <c r="D94" t="s">
-        <v>12</v>
-      </c>
-      <c r="E94">
-        <v>0.14000000000000001</v>
-      </c>
-    </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A95" t="s">
-        <v>15</v>
-      </c>
-      <c r="B95">
+      <c r="D155" t="s">
+        <v>29</v>
+      </c>
+      <c r="E155">
+        <v>3.0144997437675215E-2</v>
+      </c>
+    </row>
+    <row r="156" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A156" t="s">
+        <v>26</v>
+      </c>
+      <c r="B156">
+        <v>27</v>
+      </c>
+      <c r="C156">
+        <v>36</v>
+      </c>
+      <c r="D156" t="s">
+        <v>29</v>
+      </c>
+      <c r="E156">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="157" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A157" t="s">
+        <v>26</v>
+      </c>
+      <c r="B157">
+        <v>27</v>
+      </c>
+      <c r="C157">
+        <v>37</v>
+      </c>
+      <c r="D157" t="s">
+        <v>29</v>
+      </c>
+      <c r="E157">
+        <v>3.323031934336889E-2</v>
+      </c>
+    </row>
+    <row r="158" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A158" t="s">
+        <v>26</v>
+      </c>
+      <c r="B158">
+        <v>27</v>
+      </c>
+      <c r="C158">
+        <v>45</v>
+      </c>
+      <c r="D158" t="s">
+        <v>24</v>
+      </c>
+      <c r="E158">
+        <v>11.229837337507655</v>
+      </c>
+    </row>
+    <row r="159" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A159" t="s">
+        <v>26</v>
+      </c>
+      <c r="B159">
+        <v>27</v>
+      </c>
+      <c r="C159">
+        <v>46</v>
+      </c>
+      <c r="D159" t="s">
+        <v>24</v>
+      </c>
+      <c r="E159">
+        <v>23.619957537154985</v>
+      </c>
+    </row>
+    <row r="160" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A160" t="s">
+        <v>26</v>
+      </c>
+      <c r="B160">
+        <v>27</v>
+      </c>
+      <c r="C160">
+        <v>47</v>
+      </c>
+      <c r="D160" t="s">
         <v>25</v>
       </c>
-      <c r="C95">
-        <v>37</v>
-      </c>
-      <c r="D95" t="s">
-        <v>12</v>
-      </c>
-      <c r="E95">
-        <v>0.19</v>
-      </c>
-    </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A96" t="s">
-        <v>1</v>
-      </c>
-      <c r="B96">
-        <v>21</v>
-      </c>
-      <c r="C96">
-        <v>21</v>
-      </c>
-      <c r="D96" t="s">
-        <v>7</v>
-      </c>
-      <c r="E96">
-        <v>0.16680567139282734</v>
-      </c>
-    </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A97" t="s">
-        <v>1</v>
-      </c>
-      <c r="B97">
-        <v>92</v>
-      </c>
-      <c r="C97">
-        <v>21</v>
-      </c>
-      <c r="D97" t="s">
-        <v>7</v>
-      </c>
-      <c r="E97">
-        <v>0.02</v>
-      </c>
-    </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A98" t="s">
-        <v>1</v>
-      </c>
-      <c r="B98">
-        <v>154</v>
-      </c>
-      <c r="C98">
-        <v>21</v>
-      </c>
-      <c r="D98" t="s">
-        <v>7</v>
-      </c>
-      <c r="E98">
-        <v>0.05</v>
+      <c r="E160">
+        <v>95.876870940412317</v>
+      </c>
+    </row>
+    <row r="161" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A161" t="s">
+        <v>26</v>
+      </c>
+      <c r="B161">
+        <v>27</v>
+      </c>
+      <c r="C161">
+        <v>48</v>
+      </c>
+      <c r="D161" t="s">
+        <v>25</v>
+      </c>
+      <c r="E161">
+        <v>195.71214629147946</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E182">
-    <sortCondition ref="D2:D182"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J161">
+    <sortCondition ref="A2:A161"/>
+    <sortCondition ref="B2:B161"/>
+    <sortCondition ref="C2:C161"/>
   </sortState>
   <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
